--- a/InputData/elec/SoEDtICoS/Share of Electricity Demand that Is Cost of Service.xlsx
+++ b/InputData/elec/SoEDtICoS/Share of Electricity Demand that Is Cost of Service.xlsx
@@ -5,13 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoEDtICoS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\elec\SoEDtICoS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F607A02-5CDC-40F8-A80A-7B1787C1C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA48E77-C41B-4603-B98B-8C9B61324CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{7FFEDBA9-A430-409B-AA30-CC982E766D40}"/>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E07B5A2F-491A-4974-9CCC-AE919D973516}"/>
+    <workbookView xWindow="33795" yWindow="2025" windowWidth="26460" windowHeight="11235" xr2:uid="{E07B5A2F-491A-4974-9CCC-AE919D973516}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -63,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="165">
   <si>
     <t>Source:</t>
   </si>
@@ -555,6 +554,9 @@
   </si>
   <si>
     <t>https://www.epa.gov/system/files/documents/2021-09/chapter-3-power-system-operation-assumptions.pdf</t>
+  </si>
+  <si>
+    <t>Using 1 for all values for MX</t>
   </si>
 </sst>
 </file>
@@ -637,7 +639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -667,6 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -948,172 +951,186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="61.81640625" customWidth="1"/>
+    <col min="2" max="2" width="61.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" s="4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="4">
         <v>2018</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="4" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B13" s="4">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="4">
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B14" s="4" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="8" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="4">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="4">
         <v>2021</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="4" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="9" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="4" t="s">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B26" s="4">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="4">
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B27" s="4" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B28" s="4" t="s">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B29" s="4" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B30" s="4"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B31" s="4"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1125,13 +1142,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C915C46-25A7-483B-B849-796DAF8E3E9A}">
   <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" customWidth="1"/>
-    <col min="2" max="2" width="48.1796875" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="48.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>151</v>
       </c>
@@ -1220,7 +1237,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -1309,7 +1326,7 @@
         <v>610.92700000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1398,7 +1415,7 @@
         <v>369.35700000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
@@ -1487,7 +1504,7 @@
         <v>311.76799999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>137</v>
       </c>
@@ -1576,7 +1593,7 @@
         <v>284.084</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -1665,7 +1682,7 @@
         <v>144.916</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -1754,7 +1771,7 @@
         <v>273.37400000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -1843,7 +1860,7 @@
         <v>167.262</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1932,7 +1949,7 @@
         <v>110.102</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -2021,7 +2038,7 @@
         <v>116.28</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>141</v>
       </c>
@@ -2110,7 +2127,7 @@
         <v>395.113</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>142</v>
       </c>
@@ -2199,7 +2216,7 @@
         <v>445.13200000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>143</v>
       </c>
@@ -2288,7 +2305,7 @@
         <v>135.875</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -2377,7 +2394,7 @@
         <v>166.102</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>145</v>
       </c>
@@ -2466,7 +2483,7 @@
         <v>324.66300000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -2555,7 +2572,7 @@
         <v>337.26299999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -2644,7 +2661,7 @@
         <v>258.16300000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>133</v>
       </c>
@@ -2733,7 +2750,7 @@
         <v>214.47</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>134</v>
       </c>
@@ -2822,7 +2839,7 @@
         <v>113.884</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>135</v>
       </c>
@@ -2911,7 +2928,7 @@
         <v>85.233999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -3000,7 +3017,7 @@
         <v>219.249</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -3089,7 +3106,7 @@
         <v>201.97</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -3178,7 +3195,7 @@
         <v>234.614</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -3267,7 +3284,7 @@
         <v>305.83300000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -3356,7 +3373,7 @@
         <v>139.16499999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>148</v>
       </c>
@@ -3453,12 +3470,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6409034E-1311-4773-8646-7288B855CC12}">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -3466,7 +3483,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3489,7 +3506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>2021</v>
       </c>
@@ -3515,7 +3532,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3544,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3573,7 +3590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -3602,7 +3619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -3631,7 +3648,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3660,7 +3677,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -3689,7 +3706,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3718,7 +3735,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -3747,7 +3764,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3776,7 +3793,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3805,7 +3822,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -3834,7 +3851,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -3863,7 +3880,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3892,7 +3909,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -3921,7 +3938,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -3950,7 +3967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -3979,7 +3996,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -4008,7 +4025,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -4037,7 +4054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -4066,7 +4083,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -4095,7 +4112,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -4124,7 +4141,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -4153,7 +4170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -4182,7 +4199,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -4211,7 +4228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -4240,7 +4257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -4269,7 +4286,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -4298,7 +4315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -4327,7 +4344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -4356,7 +4373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -4385,7 +4402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -4414,7 +4431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -4443,7 +4460,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -4472,7 +4489,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -4501,7 +4518,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -4530,7 +4547,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -4559,7 +4576,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>55</v>
       </c>
@@ -4588,7 +4605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -4617,7 +4634,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -4646,7 +4663,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -4675,7 +4692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -4704,7 +4721,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -4733,7 +4750,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -4762,7 +4779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -4791,7 +4808,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -4820,7 +4837,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -4849,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -4878,7 +4895,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -4907,7 +4924,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -4936,7 +4953,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -4965,7 +4982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -4994,7 +5011,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -5023,7 +5040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>74</v>
       </c>
@@ -5052,7 +5069,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>75</v>
       </c>
@@ -5081,7 +5098,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>76</v>
       </c>
@@ -5110,7 +5127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -5139,7 +5156,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -5168,7 +5185,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -5197,7 +5214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -5226,7 +5243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>78</v>
       </c>
@@ -5255,7 +5272,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>88</v>
       </c>
@@ -5284,7 +5301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -5313,7 +5330,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>85</v>
       </c>
@@ -5342,7 +5359,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>77</v>
       </c>
@@ -5371,7 +5388,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -5400,7 +5417,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>84</v>
       </c>
@@ -5429,7 +5446,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>86</v>
       </c>
@@ -5466,14 +5483,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903608CB-714D-4908-ACA4-73ACEAE93BB0}">
   <dimension ref="A1:BV74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" customWidth="1"/>
-    <col min="2" max="3" width="13.36328125" customWidth="1"/>
-    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="3" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.3">
       <c r="F1" s="16" t="s">
         <v>150</v>
       </c>
@@ -5547,7 +5564,7 @@
       <c r="BU1" s="15"/>
       <c r="BV1" s="15"/>
     </row>
-    <row r="2" spans="1:74" s="10" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:74" s="10" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>90</v>
       </c>
@@ -5747,7 +5764,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -6015,7 +6032,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -6283,7 +6300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -6551,7 +6568,7 @@
         <v>0.83724537346020922</v>
       </c>
     </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -6819,7 +6836,7 @@
         <v>0.66898192951640811</v>
       </c>
     </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -7087,7 +7104,7 @@
         <v>0.90000000000000013</v>
       </c>
     </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -7355,7 +7372,7 @@
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -7623,7 +7640,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -7891,7 +7908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -8159,7 +8176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -8427,7 +8444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -8695,7 +8712,7 @@
         <v>0.41000000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -8963,7 +8980,7 @@
         <v>0.41000000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>32</v>
       </c>
@@ -9232,7 +9249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>32</v>
       </c>
@@ -9501,7 +9518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -9769,7 +9786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -10037,7 +10054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -10305,7 +10322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -10573,7 +10590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -10841,7 +10858,7 @@
         <v>0.99000000000000021</v>
       </c>
     </row>
-    <row r="22" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -11109,7 +11126,7 @@
         <v>0.97999999999999987</v>
       </c>
     </row>
-    <row r="23" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -11377,7 +11394,7 @@
         <v>0.90000000000000024</v>
       </c>
     </row>
-    <row r="24" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -11645,7 +11662,7 @@
         <v>0.90000000000000013</v>
       </c>
     </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -11913,7 +11930,7 @@
         <v>0.96999999999999986</v>
       </c>
     </row>
-    <row r="26" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -12181,7 +12198,7 @@
         <v>0.99717836921039082</v>
       </c>
     </row>
-    <row r="27" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -12449,7 +12466,7 @@
         <v>0.97160237320255882</v>
       </c>
     </row>
-    <row r="28" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -12527,7 +12544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -12605,7 +12622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -12683,7 +12700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -12761,7 +12778,7 @@
         <v>5.8571428571428566E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -12839,7 +12856,7 @@
         <v>8.6811224489795918E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -12917,7 +12934,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -12995,7 +13012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -13073,7 +13090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -13151,7 +13168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -13229,7 +13246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>68</v>
       </c>
@@ -13307,7 +13324,7 @@
         <v>0.26461734693877548</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -13385,7 +13402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>58</v>
       </c>
@@ -13463,7 +13480,7 @@
         <v>0.15267175572519084</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -13541,7 +13558,7 @@
         <v>0.84732824427480913</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>60</v>
       </c>
@@ -13620,7 +13637,7 @@
         <v>5.4073497229094381E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>60</v>
       </c>
@@ -13699,7 +13716,7 @@
         <v>4.200772189023981E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -13777,7 +13794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -13855,7 +13872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>64</v>
       </c>
@@ -13933,7 +13950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -14011,7 +14028,7 @@
         <v>0.57035530562136616</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -14089,7 +14106,7 @@
         <v>0.17706966277858127</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -14167,7 +14184,7 @@
         <v>0.38951094042434764</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -14245,7 +14262,7 @@
         <v>0.78092261533117902</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>80</v>
       </c>
@@ -14323,7 +14340,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -14401,7 +14418,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -14479,7 +14496,7 @@
         <v>0.15352941176470589</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -14557,7 +14574,7 @@
         <v>0.12176470588235294</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>87</v>
       </c>
@@ -14635,7 +14652,7 @@
         <v>0.67240329109177721</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -14713,7 +14730,7 @@
         <v>0.90534977569328257</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>81</v>
       </c>
@@ -14791,7 +14808,7 @@
         <v>0.25318722053020237</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -14869,7 +14886,7 @@
         <v>3.0018004066597201E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>78</v>
       </c>
@@ -14947,7 +14964,7 @@
         <v>6.7990654205607473E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -15025,7 +15042,7 @@
         <v>0.17410442358626374</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>82</v>
       </c>
@@ -15103,7 +15120,7 @@
         <v>0.13633158028549358</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>85</v>
       </c>
@@ -15181,7 +15198,7 @@
         <v>0.90200934579439251</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -15259,7 +15276,7 @@
         <v>0.62470588235294122</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>83</v>
       </c>
@@ -15338,7 +15355,7 @@
         <v>0.15509812843952783</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>83</v>
       </c>
@@ -15417,7 +15434,7 @@
         <v>0.10347428125536176</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>84</v>
       </c>
@@ -15495,7 +15512,7 @@
         <v>0.31161504065255674</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>86</v>
       </c>
@@ -15574,7 +15591,7 @@
         <v>0.11535066405588799</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>86</v>
       </c>
@@ -15653,12 +15670,12 @@
         <v>9.181071757751591E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>32</v>
       </c>
@@ -15707,7 +15724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>60</v>
       </c>
@@ -15756,7 +15773,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -15805,7 +15822,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -15875,16 +15892,16 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="26" width="10.453125" customWidth="1"/>
-    <col min="27" max="27" width="13.26953125" customWidth="1"/>
-    <col min="28" max="28" width="11.26953125" customWidth="1"/>
-    <col min="29" max="31" width="10.453125" customWidth="1"/>
+    <col min="2" max="26" width="10.44140625" customWidth="1"/>
+    <col min="27" max="27" width="13.21875" customWidth="1"/>
+    <col min="28" max="28" width="11.21875" customWidth="1"/>
+    <col min="29" max="31" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -15979,132 +15996,102 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="14">
-        <f>$E$2</f>
-        <v>0.68934721150190648</v>
+        <v>1</v>
       </c>
       <c r="C2" s="14">
-        <f t="shared" ref="C2:D2" si="0">$E$2</f>
-        <v>0.68934721150190648</v>
+        <v>1</v>
       </c>
       <c r="D2" s="14">
-        <f t="shared" si="0"/>
-        <v>0.68934721150190648</v>
+        <v>1</v>
       </c>
       <c r="E2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!C2:C26,'Cost-of-Service Shares'!AV3:AV27)/SUM('NEMS Net Load'!C2:C26)</f>
-        <v>0.68934721150190648</v>
+        <v>1</v>
       </c>
       <c r="F2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!D2:D26,'Cost-of-Service Shares'!AW3:AW27)/SUM('NEMS Net Load'!D2:D26)</f>
-        <v>0.68807244878773488</v>
+        <v>1</v>
       </c>
       <c r="G2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!E2:E26,'Cost-of-Service Shares'!AX3:AX27)/SUM('NEMS Net Load'!E2:E26)</f>
-        <v>0.68849464943480909</v>
+        <v>1</v>
       </c>
       <c r="H2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!F2:F26,'Cost-of-Service Shares'!AY3:AY27)/SUM('NEMS Net Load'!F2:F26)</f>
-        <v>0.68859975876651858</v>
+        <v>1</v>
       </c>
       <c r="I2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!G2:G26,'Cost-of-Service Shares'!AZ3:AZ27)/SUM('NEMS Net Load'!G2:G26)</f>
-        <v>0.68877964764386135</v>
+        <v>1</v>
       </c>
       <c r="J2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!H2:H26,'Cost-of-Service Shares'!BA3:BA27)/SUM('NEMS Net Load'!H2:H26)</f>
-        <v>0.68881037018673585</v>
+        <v>1</v>
       </c>
       <c r="K2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!I2:I26,'Cost-of-Service Shares'!BB3:BB27)/SUM('NEMS Net Load'!I2:I26)</f>
-        <v>0.68907451539154441</v>
+        <v>1</v>
       </c>
       <c r="L2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!J2:J26,'Cost-of-Service Shares'!BC3:BC27)/SUM('NEMS Net Load'!J2:J26)</f>
-        <v>0.68939660023132276</v>
+        <v>1</v>
       </c>
       <c r="M2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!K2:K26,'Cost-of-Service Shares'!BD3:BD27)/SUM('NEMS Net Load'!K2:K26)</f>
-        <v>0.68970854784480562</v>
+        <v>1</v>
       </c>
       <c r="N2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!L2:L26,'Cost-of-Service Shares'!BE3:BE27)/SUM('NEMS Net Load'!L2:L26)</f>
-        <v>0.69025610041253971</v>
+        <v>1</v>
       </c>
       <c r="O2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!M2:M26,'Cost-of-Service Shares'!BF3:BF27)/SUM('NEMS Net Load'!M2:M26)</f>
-        <v>0.69079376668380665</v>
+        <v>1</v>
       </c>
       <c r="P2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!N2:N26,'Cost-of-Service Shares'!BG3:BG27)/SUM('NEMS Net Load'!N2:N26)</f>
-        <v>0.69131976731724487</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!O2:O26,'Cost-of-Service Shares'!BH3:BH27)/SUM('NEMS Net Load'!O2:O26)</f>
-        <v>0.69165683041367332</v>
+        <v>1</v>
       </c>
       <c r="R2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!P2:P26,'Cost-of-Service Shares'!BI3:BI27)/SUM('NEMS Net Load'!P2:P26)</f>
-        <v>0.69178235361908935</v>
+        <v>1</v>
       </c>
       <c r="S2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!Q2:Q26,'Cost-of-Service Shares'!BJ3:BJ27)/SUM('NEMS Net Load'!Q2:Q26)</f>
-        <v>0.69196354580560815</v>
+        <v>1</v>
       </c>
       <c r="T2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!R2:R26,'Cost-of-Service Shares'!BK3:BK27)/SUM('NEMS Net Load'!R2:R26)</f>
-        <v>0.69211680559681221</v>
+        <v>1</v>
       </c>
       <c r="U2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!S2:S26,'Cost-of-Service Shares'!BL3:BL27)/SUM('NEMS Net Load'!S2:S26)</f>
-        <v>0.69237808127570022</v>
+        <v>1</v>
       </c>
       <c r="V2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!T2:T26,'Cost-of-Service Shares'!BM3:BM27)/SUM('NEMS Net Load'!T2:T26)</f>
-        <v>0.69268389142927922</v>
+        <v>1</v>
       </c>
       <c r="W2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!U2:U26,'Cost-of-Service Shares'!BN3:BN27)/SUM('NEMS Net Load'!U2:U26)</f>
-        <v>0.69296954018079393</v>
+        <v>1</v>
       </c>
       <c r="X2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!V2:V26,'Cost-of-Service Shares'!BO3:BO27)/SUM('NEMS Net Load'!V2:V26)</f>
-        <v>0.69316974948547416</v>
+        <v>1</v>
       </c>
       <c r="Y2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!W2:W26,'Cost-of-Service Shares'!BP3:BP27)/SUM('NEMS Net Load'!W2:W26)</f>
-        <v>0.69332209222553232</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!X2:X26,'Cost-of-Service Shares'!BQ3:BQ27)/SUM('NEMS Net Load'!X2:X26)</f>
-        <v>0.69346289820683571</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!Y2:Y26,'Cost-of-Service Shares'!BR3:BR27)/SUM('NEMS Net Load'!Y2:Y26)</f>
-        <v>0.6935141246138693</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!Z2:Z26,'Cost-of-Service Shares'!BS3:BS27)/SUM('NEMS Net Load'!Z2:Z26)</f>
-        <v>0.69376790151411949</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!AA2:AA26,'Cost-of-Service Shares'!BT3:BT27)/SUM('NEMS Net Load'!AA2:AA26)</f>
-        <v>0.69406775650288999</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!AB2:AB26,'Cost-of-Service Shares'!BU3:BU27)/SUM('NEMS Net Load'!AB2:AB26)</f>
-        <v>0.69437668751431925</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="14">
-        <f>SUMPRODUCT('NEMS Net Load'!AC2:AC26,'Cost-of-Service Shares'!BV3:BV27)/SUM('NEMS Net Load'!AC2:AC26)</f>
-        <v>0.69462189821419851</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="F10" s="3"/>
     </row>
   </sheetData>

--- a/InputData/elec/SoEDtICoS/Share of Electricity Demand that Is Cost of Service.xlsx
+++ b/InputData/elec/SoEDtICoS/Share of Electricity Demand that Is Cost of Service.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\elec\SoEDtICoS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA48E77-C41B-4603-B98B-8C9B61324CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066FDBAA-B051-45A0-9238-2A09D44B7340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33795" yWindow="2025" windowWidth="26460" windowHeight="11235" xr2:uid="{E07B5A2F-491A-4974-9CCC-AE919D973516}"/>
+    <workbookView xWindow="696" yWindow="372" windowWidth="19536" windowHeight="13104" activeTab="4" xr2:uid="{E07B5A2F-491A-4974-9CCC-AE919D973516}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -639,7 +639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -669,7 +669,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -966,7 +965,7 @@
       <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" t="s">
         <v>164</v>
       </c>
     </row>
@@ -15891,7 +15890,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -15901,7 +15900,7 @@
     <col min="29" max="31" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -15995,8 +15994,75 @@
       <c r="AE1" s="5">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF1" s="5">
+        <v>2051</v>
+      </c>
+      <c r="AG1" s="5">
+        <v>2052</v>
+      </c>
+      <c r="AH1" s="5">
+        <v>2053</v>
+      </c>
+      <c r="AI1" s="5">
+        <v>2054</v>
+      </c>
+      <c r="AJ1" s="5">
+        <v>2055</v>
+      </c>
+      <c r="AK1" s="5">
+        <v>2056</v>
+      </c>
+      <c r="AL1" s="5">
+        <v>2057</v>
+      </c>
+      <c r="AM1" s="5">
+        <v>2058</v>
+      </c>
+      <c r="AN1" s="5">
+        <v>2059</v>
+      </c>
+      <c r="AO1" s="5">
+        <v>2060</v>
+      </c>
+      <c r="AP1" s="5">
+        <v>2061</v>
+      </c>
+      <c r="AQ1" s="5">
+        <v>2062</v>
+      </c>
+      <c r="AR1" s="5">
+        <v>2063</v>
+      </c>
+      <c r="AS1" s="5">
+        <v>2064</v>
+      </c>
+      <c r="AT1" s="5">
+        <v>2065</v>
+      </c>
+      <c r="AU1" s="5">
+        <v>2066</v>
+      </c>
+      <c r="AV1" s="5">
+        <v>2067</v>
+      </c>
+      <c r="AW1" s="5">
+        <v>2068</v>
+      </c>
+      <c r="AX1" s="5">
+        <v>2069</v>
+      </c>
+      <c r="AY1" s="5">
+        <v>2070</v>
+      </c>
+      <c r="AZ1" s="5"/>
+      <c r="BA1" s="5"/>
+      <c r="BB1" s="5"/>
+      <c r="BC1" s="5"/>
+      <c r="BD1" s="5"/>
+      <c r="BE1" s="5"/>
+      <c r="BF1" s="5"/>
+    </row>
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -16090,8 +16156,68 @@
       <c r="AE2" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AU2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="14">
+        <v>1</v>
+      </c>
+      <c r="AY2" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="F10" s="3"/>
     </row>
   </sheetData>
